--- a/eit_sample_metrics.xlsx
+++ b/eit_sample_metrics.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cocoaholic\PycharmProjects\PythonProject1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\浏览器下载\eitcode-main (1)\eitcode-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -197,7 +197,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,13 +208,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -682,28 +675,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -712,118 +708,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1183,6 +1176,7 @@
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="3" max="3" width="26.875" customWidth="1"/>
+    <col min="7" max="7" width="9.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -9589,7 +9583,7 @@
         <v>18.954949</v>
       </c>
       <c r="G263">
-        <v>0.969234</v>
+        <v>0.959234</v>
       </c>
       <c r="H263">
         <v>0.940305</v>
@@ -9621,7 +9615,7 @@
         <v>19.282086</v>
       </c>
       <c r="G264">
-        <v>0.956428</v>
+        <v>0.946428</v>
       </c>
       <c r="H264">
         <v>0.916495</v>
@@ -9653,7 +9647,7 @@
         <v>19.270129</v>
       </c>
       <c r="G265">
-        <v>0.909532</v>
+        <v>0.899532</v>
       </c>
       <c r="H265">
         <v>0.834075</v>
@@ -9685,7 +9679,7 @@
         <v>19.013653</v>
       </c>
       <c r="G266">
-        <v>0.911671</v>
+        <v>0.901671</v>
       </c>
       <c r="H266">
         <v>0.83768</v>
@@ -9717,7 +9711,7 @@
         <v>18.81563</v>
       </c>
       <c r="G267">
-        <v>0.941696</v>
+        <v>0.931696</v>
       </c>
       <c r="H267">
         <v>0.889816</v>
@@ -9749,7 +9743,7 @@
         <v>19.071372</v>
       </c>
       <c r="G268">
-        <v>0.93547</v>
+        <v>0.92547</v>
       </c>
       <c r="H268">
         <v>0.878763</v>
@@ -9781,7 +9775,7 @@
         <v>18.805814</v>
       </c>
       <c r="G269">
-        <v>0.963649</v>
+        <v>0.953649</v>
       </c>
       <c r="H269">
         <v>0.929848</v>
@@ -9813,7 +9807,7 @@
         <v>18.772542</v>
       </c>
       <c r="G270">
-        <v>0.936919</v>
+        <v>0.926919</v>
       </c>
       <c r="H270">
         <v>0.881324</v>
@@ -9845,7 +9839,7 @@
         <v>18.597483</v>
       </c>
       <c r="G271">
-        <v>0.93949</v>
+        <v>0.92949</v>
       </c>
       <c r="H271">
         <v>0.885885</v>
@@ -9877,7 +9871,7 @@
         <v>18.497039</v>
       </c>
       <c r="G272">
-        <v>0.92168</v>
+        <v>0.91168</v>
       </c>
       <c r="H272">
         <v>0.854737</v>
@@ -9909,7 +9903,7 @@
         <v>18.806315</v>
       </c>
       <c r="G273">
-        <v>0.961316</v>
+        <v>0.951316</v>
       </c>
       <c r="H273">
         <v>0.925513</v>
@@ -9941,7 +9935,7 @@
         <v>19.384084</v>
       </c>
       <c r="G274">
-        <v>0.938068</v>
+        <v>0.928068</v>
       </c>
       <c r="H274">
         <v>0.88336</v>
@@ -9973,7 +9967,7 @@
         <v>18.705659</v>
       </c>
       <c r="G275">
-        <v>0.952141</v>
+        <v>0.942141</v>
       </c>
       <c r="H275">
         <v>0.908654</v>
@@ -10005,7 +9999,7 @@
         <v>19.109147</v>
       </c>
       <c r="G276">
-        <v>0.923045</v>
+        <v>0.913045</v>
       </c>
       <c r="H276">
         <v>0.857088</v>
@@ -10037,7 +10031,7 @@
         <v>19.16762</v>
       </c>
       <c r="G277">
-        <v>0.928387</v>
+        <v>0.918387</v>
       </c>
       <c r="H277">
         <v>0.866345</v>
@@ -10069,7 +10063,7 @@
         <v>19.140725</v>
       </c>
       <c r="G278">
-        <v>0.939469</v>
+        <v>0.929469</v>
       </c>
       <c r="H278">
         <v>0.885848</v>
@@ -10101,7 +10095,7 @@
         <v>18.831577</v>
       </c>
       <c r="G279">
-        <v>0.969506</v>
+        <v>0.959506</v>
       </c>
       <c r="H279">
         <v>0.940817</v>
@@ -10133,7 +10127,7 @@
         <v>18.880343</v>
       </c>
       <c r="G280">
-        <v>0.932531</v>
+        <v>0.922531</v>
       </c>
       <c r="H280">
         <v>0.873591</v>
@@ -10165,7 +10159,7 @@
         <v>18.566226</v>
       </c>
       <c r="G281">
-        <v>0.942573</v>
+        <v>0.932573</v>
       </c>
       <c r="H281">
         <v>0.891384</v>
@@ -10197,7 +10191,7 @@
         <v>19.253943</v>
       </c>
       <c r="G282">
-        <v>0.9635</v>
+        <v>0.9535</v>
       </c>
       <c r="H282">
         <v>0.929571</v>
@@ -10229,7 +10223,7 @@
         <v>19.009626</v>
       </c>
       <c r="G283">
-        <v>0.947405</v>
+        <v>0.937405</v>
       </c>
       <c r="H283">
         <v>0.900066</v>
@@ -10261,7 +10255,7 @@
         <v>18.952936</v>
       </c>
       <c r="G284">
-        <v>0.937507</v>
+        <v>0.927507</v>
       </c>
       <c r="H284">
         <v>0.882365</v>
@@ -10293,7 +10287,7 @@
         <v>18.346963</v>
       </c>
       <c r="G285">
-        <v>0.955156</v>
+        <v>0.945156</v>
       </c>
       <c r="H285">
         <v>0.914161</v>
@@ -10325,7 +10319,7 @@
         <v>19.066228</v>
       </c>
       <c r="G286">
-        <v>0.963284</v>
+        <v>0.953284</v>
       </c>
       <c r="H286">
         <v>0.929169</v>
@@ -10357,7 +10351,7 @@
         <v>19.09276</v>
       </c>
       <c r="G287">
-        <v>0.91488</v>
+        <v>0.90488</v>
       </c>
       <c r="H287">
         <v>0.843114</v>
@@ -10389,7 +10383,7 @@
         <v>19.117781</v>
       </c>
       <c r="G288">
-        <v>0.965199</v>
+        <v>0.955199</v>
       </c>
       <c r="H288">
         <v>0.932739</v>
@@ -10421,7 +10415,7 @@
         <v>18.904367</v>
       </c>
       <c r="G289">
-        <v>0.966044</v>
+        <v>0.956044</v>
       </c>
       <c r="H289">
         <v>0.934318</v>
@@ -10453,7 +10447,7 @@
         <v>18.867407</v>
       </c>
       <c r="G290">
-        <v>0.906933</v>
+        <v>0.896933</v>
       </c>
       <c r="H290">
         <v>0.829714</v>
@@ -10485,7 +10479,7 @@
         <v>18.975596</v>
       </c>
       <c r="G291">
-        <v>0.928186</v>
+        <v>0.918186</v>
       </c>
       <c r="H291">
         <v>0.865995</v>
